--- a/forms/trg/Formulir_TRG_marsplan.xlsx
+++ b/forms/trg/Formulir_TRG_marsplan.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Ahmad Faizal</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -951,7 +955,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -988,7 +992,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1025,7 +1029,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1062,7 +1066,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1099,7 +1103,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1136,7 +1140,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1173,7 +1177,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1206,7 +1210,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1243,7 +1247,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1313,7 +1317,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1346,7 +1350,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
